--- a/TDD_examples/CASE_1_ITER_like_LTS/conductor_1_operation.xlsx
+++ b/TDD_examples/CASE_1_ITER_like_LTS/conductor_1_operation.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="4" r:id="Rc5d67577fa8546d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R83785f9f63124212"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Rb8d2a623a5164319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="Rd3bbbf62efcb4afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="2" r:id="Rcdd0e9934ada4a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="4" r:id="R79d64b19d0c54887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R454c2dcc6cda4786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="Rc1296567f9dc4210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R07c544e0da6c49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="2" r:id="R737ce05ab3bf46e7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -681,7 +681,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D4" s="62" t="str">
-        <x:v>flag to define initialization and the hydraulic boundary conditions (&gt;0 value from below, &lt;0 valure from input file: press.dat, temp.dat, mdot.dat). 1 = inlet and outlet pressure, inlet (outlet) temperaure; 2 = inlet pressure and temperature, outlet mass flow rate; 3 = inlet mass flow rate and temperature, outlet pressure.</x:v>
+        <x:v>Flag used to define the initialization and hydraulic boundary conditions (&gt; 0: use the values below; &lt; 0: read values from the input files press.dat, temp.dat, and mdot.dat). 1 = inlet and outlet pressure, and inlet (outlet) temperature; 2 = inlet pressure and temperature, and outlet mass flow rate; 3 = inlet mass flow rate and temperature, and outlet pressure.</x:v>
       </x:c>
       <x:c r="E4" s="61" t="n">
         <x:v>3</x:v>
@@ -821,7 +821,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>flag to define the flow direction. Possible values: forward or Forward or FORWARD (inlet at x  = 0 and outlet at x = L); backward or Backward or BACKWARD (inlet at x = L and outlet at x = 0). Defaults to forward. If chanels are in hydraulic parallel, they must all have the same flow direction.</x:v>
+        <x:v>Flag used to define the flow direction. Possible values: forward, Forward, or FORWARD (inlet at x = 0 and outlet at x = L); backward, Backward, or BACKWARD (inlet at x = L and outlet at x = 0). Defaults to forward. Channels in hydraulic parallel must all have the same flow direction.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>forward</x:v>
@@ -937,7 +937,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -954,7 +954,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D6" s="62" t="str">
-        <x:v>Flag to allow user to specify the potential value in some axial location of the conductor. Possible values: 1 = user can assign the position and the value of the potential; 0 = user can not assign these values. Defaults to 0</x:v>
+        <x:v>Flag used to allow the user to specify potential values at selected axial locations of the conductor. Possible values: 1 = the user can assign the locations and potential values; 0 = the user cannot assign these values. Defaults to 0.</x:v>
       </x:c>
       <x:c r="E6" s="78" t="n">
         <x:v>0</x:v>
@@ -988,7 +988,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="62" t="str">
-        <x:v>List of axial coordinate at which assing the fix potential value, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if at z = 0.5m z = 1.0m and z = 1.5m user wants to fix the potential value, write 0.5,1.0,1.5.</x:v>
+        <x:v>List of axial coordinates at which the fixed potential values are assigned, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to fix the potential at z = 0.5 m, 1.0 m, and 1.5 m, enter 0.5,1.0,1.5.</x:v>
       </x:c>
       <x:c r="E8" s="61" t="n">
         <x:v>0</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>List of fix potential value the user wants to assig, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if user wants to assign three potential values, write: 0.0,2.0,4.0.</x:v>
+        <x:v>List of fixed potential values, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to assign three potential values, enter 0.0,2.0,4.0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -1039,7 +1039,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>linear</x:v>
@@ -1073,7 +1073,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D13" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="n">
         <x:v>1</x:v>
@@ -1090,7 +1090,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="n">
         <x:v>1</x:v>
@@ -1124,7 +1124,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E16" s="61" t="str">
         <x:v>linear</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D21" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E21" s="61" t="str">
         <x:v>linear</x:v>
@@ -1277,7 +1277,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D25" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E25" s="61" t="n">
         <x:v>0</x:v>
@@ -1362,7 +1362,7 @@
         <x:v>bool</x:v>
       </x:c>
       <x:c r="D30" s="62" t="str">
-        <x:v>Flag to decide if the current sharing temperature should be evaluated at each time steps or not (improve speed). Possible values: False = evaluate the current sharing temperature only at the initialization and at the end of the simulation; True = evaluate the current sharing temperature at each time steps (affects computaion time). Defaults to False.</x:v>
+        <x:v>Flag used to determine whether the current-sharing temperature is evaluated at every time step. Possible values: False = evaluate it only during initialization and at the end of the simulation; True = evaluate it at every time step (increases computation time). Defaults to False.</x:v>
       </x:c>
       <x:c r="E30" s="79" t="b">
         <x:v>0</x:v>
@@ -1487,7 +1487,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -1504,7 +1504,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D6" s="62" t="str">
-        <x:v>Flag to allow user to specify the potential value in some axial location of the conductor. Possible values: 1 = user can assign the position and the value of the potential; 0 = user can not assign these values. Defaults to 0</x:v>
+        <x:v>Flag used to allow the user to specify potential values at selected axial locations of the conductor. Possible values: 1 = the user can assign the locations and potential values; 0 = the user cannot assign these values. Defaults to 0.</x:v>
       </x:c>
       <x:c r="E6" s="78" t="n">
         <x:v>0</x:v>
@@ -1538,7 +1538,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="62" t="str">
-        <x:v>List of axial coordinate at which assing the fix potential value, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if at z = 0.5m z = 1.0m and z = 1.5m user wants to fix the potential value, write 0.5,1.0,1.5.</x:v>
+        <x:v>List of axial coordinates at which the fixed potential values are assigned, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to fix the potential at z = 0.5 m, 1.0 m, and 1.5 m, enter 0.5,1.0,1.5.</x:v>
       </x:c>
       <x:c r="E8" s="61" t="n">
         <x:v>0</x:v>
@@ -1555,7 +1555,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>List of fix potential value the user wants to assig, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if user wants to assign three potential values, write: 0.0,2.0,4.0.</x:v>
+        <x:v>List of fixed potential values, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to assign three potential values, enter 0.0,2.0,4.0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -1589,7 +1589,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>linear</x:v>
@@ -1623,7 +1623,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D13" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="n">
         <x:v>12</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="n">
         <x:v>12</x:v>
@@ -1674,7 +1674,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E16" s="61" t="str">
         <x:v>linear</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D21" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E21" s="61" t="str">
         <x:v>linear</x:v>
@@ -1827,7 +1827,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D25" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E25" s="61" t="n">
         <x:v>6</x:v>
@@ -1912,7 +1912,7 @@
         <x:v>bool</x:v>
       </x:c>
       <x:c r="D30" s="62" t="str">
-        <x:v>Flag to decide if the current sharing temperature should be evaluated at each time steps or not (improve speed). Possible values: False = evaluate the current sharing temperature only at the initialization and at the end of the simulation; True = evaluate the current sharing temperature at each time steps (affects computaion time). Defaults to False.</x:v>
+        <x:v>Flag used to determine whether the current-sharing temperature is evaluated at every time step. Possible values: False = evaluate it only during initialization and at the end of the simulation; True = evaluate it at every time step (increases computation time). Defaults to False.</x:v>
       </x:c>
       <x:c r="E30" s="79" t="b">
         <x:v>0</x:v>
@@ -2037,7 +2037,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -2054,7 +2054,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="D6" s="62" t="str">
-        <x:v>Flag to allow user to specify the potential value in some axial location of the conductor. Possible values: 1 = user can assign the position and the value of the potential; 0 = user can not assign these values. Defaults to 0</x:v>
+        <x:v>Flag used to allow the user to specify potential values at selected axial locations of the conductor. Possible values: 1 = the user can assign the locations and potential values; 0 = the user cannot assign these values. Defaults to 0.</x:v>
       </x:c>
       <x:c r="E6" s="78" t="n">
         <x:v>0</x:v>
@@ -2088,7 +2088,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="62" t="str">
-        <x:v>List of axial coordinate at which assing the fix potential value, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if at z = 0.5m z = 1.0m and z = 1.5m user wants to fix the potential value, write 0.5,1.0,1.5.</x:v>
+        <x:v>List of axial coordinates at which the fixed potential values are assigned, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to fix the potential at z = 0.5 m, 1.0 m, and 1.5 m, enter 0.5,1.0,1.5.</x:v>
       </x:c>
       <x:c r="E8" s="61" t="n">
         <x:v>0</x:v>
@@ -2105,7 +2105,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>List of fix potential value the user wants to assig, separated by a comma, if FIX_POTENTIAL_FLAG is True. Ex, if user wants to assign three potential values, write: 0.0,2.0,4.0.</x:v>
+        <x:v>List of fixed potential values, separated by commas, if FIX_POTENTIAL_FLAG is True. For example, to assign three potential values, enter 0.0,2.0,4.0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -2139,7 +2139,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D11" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E11" s="61" t="str">
         <x:v>linear</x:v>
@@ -2173,7 +2173,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D13" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E13" s="61" t="n">
         <x:v>0</x:v>
@@ -2190,7 +2190,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="n">
         <x:v>0</x:v>
@@ -2224,7 +2224,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D16" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E16" s="61" t="str">
         <x:v>linear</x:v>
@@ -2258,7 +2258,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D18" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E18" s="61" t="str">
         <x:v>linear</x:v>
@@ -2326,7 +2326,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D22" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E22" s="61" t="n">
         <x:v>0</x:v>
@@ -2519,7 +2519,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D5" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the operating current data, if IOP_MODE = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the operating-current data when IOP_MODE = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E5" s="61" t="str">
         <x:v>linear</x:v>
@@ -2553,7 +2553,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D7" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field data, if IBFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field data when IBIFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E7" s="61" t="str">
         <x:v>linear</x:v>
@@ -2587,7 +2587,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D9" s="62" t="str">
-        <x:v>magnetic field value at x = 0 m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = 0 m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E9" s="61" t="n">
         <x:v>0</x:v>
@@ -2604,7 +2604,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D10" s="62" t="str">
-        <x:v>magnetic field value at x = L m, constant in time. Used if IBFUN = 0.</x:v>
+        <x:v>Magnetic-field value at x = L m, constant in time. Used if IBIFUN = 0.</x:v>
       </x:c>
       <x:c r="E10" s="61" t="n">
         <x:v>0</x:v>
@@ -2638,7 +2638,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D12" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the magnetic field gradient data, if IALPHAB = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the magnetic-field-gradient data when IALPHAB = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E12" s="61" t="str">
         <x:v>linear</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="D14" s="62" t="str">
-        <x:v>Flag to specify the kind of interpolator for the heat data, if IQFUN = -1. Possible values: linear = liear interpolation; cubic = use spline function of third order.</x:v>
+        <x:v>Flag used to specify the interpolation method for the heat data when IQFUN = -1. Possible values: linear = linear interpolation; cubic = third-order spline interpolation.</x:v>
       </x:c>
       <x:c r="E14" s="61" t="str">
         <x:v>linear</x:v>
@@ -2740,7 +2740,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D18" s="62" t="str">
-        <x:v>heating start time. Recommended: add the time at with the heating starts also if the heat is from external file, IQFUN = -1 (requested for the correct evaluation of htc between fluid and solid)</x:v>
+        <x:v>Heating start time. Specify this time even when the heat is read from an external file (IQFUN = -1); it is required for the correct evaluation of the HTC between the fluid and the solid.</x:v>
       </x:c>
       <x:c r="E18" s="61" t="n">
         <x:v>0</x:v>
